--- a/data/closes/2026-09-30/paquete_cierre_2026-09-30.xlsx
+++ b/data/closes/2026-09-30/paquete_cierre_2026-09-30.xlsx
@@ -31,7 +31,8 @@
     </font>
     <font>
       <b val="1"/>
-      <sz val="14"/>
+      <color rgb="007808FE"/>
+      <sz val="16"/>
     </font>
     <font>
       <b val="1"/>
@@ -45,7 +46,7 @@
       <u val="single"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill/>
     </fill>
@@ -54,7 +55,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="003F4A5A"/>
+        <fgColor rgb="007808FE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F2E6FF"/>
       </patternFill>
     </fill>
   </fills>
@@ -70,7 +76,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -79,6 +85,7 @@
     </xf>
     <xf numFmtId="4" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment wrapText="1"/>
     </xf>
@@ -156,6 +163,36 @@
     </indexedColors>
   </colors>
 </styleSheet>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>0</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="676275" cy="381000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="1" name="Image 1" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -444,10 +481,11 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
+    <tabColor rgb="007808FE"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L19"/>
+  <dimension ref="A2:L20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -464,170 +502,129 @@
     <col width="60" customWidth="1" min="12" max="12"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+    <row r="1" ht="34" customHeight="1"/>
+    <row r="2">
+      <c r="A2" s="1" t="inlineStr">
         <is>
           <t>Cierre trimestral wFIAT al 30/09/2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>Demo independiente para Ripio, por Máximo Sckell. No es una herramienta oficial.</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Corte: 30/09/2026 23:59:59 hora de Buenos Aires. Cierre anterior: 30/06/2026. Generado: 2026-10-01T20:34:51+00:00 (UTC).</t>
+          <t>Demo independiente para Ripio, por Máximo Sckell. No es una herramienta oficial.</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="inlineStr">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Corte: 30/09/2026 23:59:59 hora de Buenos Aires. Cierre anterior: 30/06/2026. Generado: 2026-10-01T21:07:02+00:00 (UTC).</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
         <is>
           <t>Conciliación por red: todas las diferencias son cero.</t>
         </is>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" s="3" t="inlineStr">
+    <row r="7">
+      <c r="A7" s="3" t="inlineStr">
         <is>
           <t>Token</t>
         </is>
       </c>
-      <c r="B6" s="3" t="inlineStr">
+      <c r="B7" s="3" t="inlineStr">
         <is>
           <t>Saldo al 30/06/2026</t>
         </is>
       </c>
-      <c r="C6" s="3" t="inlineStr">
+      <c r="C7" s="3" t="inlineStr">
         <is>
           <t>Emisiones</t>
         </is>
       </c>
-      <c r="D6" s="3" t="inlineStr">
+      <c r="D7" s="3" t="inlineStr">
         <is>
           <t>Quemas</t>
         </is>
       </c>
-      <c r="E6" s="3" t="inlineStr">
+      <c r="E7" s="3" t="inlineStr">
         <is>
           <t>Saldo al 30/09/2026</t>
         </is>
       </c>
-      <c r="F6" s="3" t="inlineStr">
+      <c r="F7" s="3" t="inlineStr">
         <is>
           <t>Variación</t>
         </is>
       </c>
-      <c r="G6" s="3" t="inlineStr">
+      <c r="G7" s="3" t="inlineStr">
         <is>
           <t>Emisión primaria</t>
         </is>
       </c>
-      <c r="H6" s="3" t="inlineStr">
+      <c r="H7" s="3" t="inlineStr">
         <is>
           <t>Rescate primario</t>
         </is>
       </c>
-      <c r="I6" s="3" t="inlineStr">
+      <c r="I7" s="3" t="inlineStr">
         <is>
           <t>Puente, entradas</t>
         </is>
       </c>
-      <c r="J6" s="3" t="inlineStr">
+      <c r="J7" s="3" t="inlineStr">
         <is>
           <t>Puente, salidas</t>
         </is>
       </c>
-      <c r="K6" s="3" t="inlineStr">
+      <c r="K7" s="3" t="inlineStr">
         <is>
           <t>Sin clasificar</t>
         </is>
       </c>
-      <c r="L6" s="3" t="inlineStr">
+      <c r="L7" s="3" t="inlineStr">
         <is>
           <t>Redes con saldo</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>wARS</t>
-        </is>
-      </c>
-      <c r="B7" s="4" t="n">
-        <v>7619996077.038589</v>
-      </c>
-      <c r="C7" s="4" t="n">
-        <v>10327488513.02053</v>
-      </c>
-      <c r="D7" s="4" t="n">
-        <v>3016290001.132575</v>
-      </c>
-      <c r="E7" s="4" t="n">
-        <v>14931194588.92655</v>
-      </c>
-      <c r="F7" s="4" t="n">
-        <v>7311198511.887959</v>
-      </c>
-      <c r="G7" s="4" t="n">
-        <v>9729100030</v>
-      </c>
-      <c r="H7" s="4" t="n">
-        <v>2458000010</v>
-      </c>
-      <c r="I7" s="4" t="n">
-        <v>558288483.0205343</v>
-      </c>
-      <c r="J7" s="4" t="n">
-        <v>558289953.0205343</v>
-      </c>
-      <c r="K7" t="n">
-        <v>4</v>
-      </c>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>Ethereum, Base, Polygon, Gnosis, BNB Smart Chain, World Chain, Celo, HyperEVM, Arc</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>wBRL</t>
+          <t>wARS</t>
         </is>
       </c>
       <c r="B8" s="4" t="n">
-        <v>2586147.5</v>
+        <v>7619996077.038589</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>12073335.11812912</v>
+        <v>10327488513.02053</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>852005.2381291243</v>
+        <v>3016290001.132575</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>13807477.38</v>
+        <v>14931194588.92655</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>11221329.88</v>
+        <v>7311198511.887959</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>11261295</v>
+        <v>9769200030</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>155000</v>
+        <v>2458000010</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>677040.1181291243</v>
+        <v>558288483.0205343</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>697005.2381291243</v>
+        <v>558289953.0205343</v>
       </c>
       <c r="K8" t="n">
         <v>2</v>
@@ -641,77 +638,77 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>wMXN</t>
+          <t>wBRL</t>
         </is>
       </c>
       <c r="B9" s="4" t="n">
-        <v>968788.69309</v>
+        <v>2586147.5</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>4760418.983088754</v>
+        <v>12073335.11812912</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>90418.9830887545</v>
+        <v>852005.2381291243</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>5638788.69309</v>
+        <v>13807477.38</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>4670000</v>
+        <v>11221329.88</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>4670000</v>
+        <v>11396295</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>0</v>
+        <v>155000</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>90418.9830887545</v>
+        <v>677040.1181291243</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>90418.9830887545</v>
+        <v>697005.2381291243</v>
       </c>
       <c r="K9" t="n">
         <v>0</v>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>Ethereum, Base, Polygon, Gnosis, BNB Smart Chain, World Chain, Celo</t>
+          <t>Ethereum, Base, Polygon, Gnosis, BNB Smart Chain, World Chain, Celo, HyperEVM, Arc</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>wCOP</t>
+          <t>wMXN</t>
         </is>
       </c>
       <c r="B10" s="4" t="n">
-        <v>196398753.7968985</v>
+        <v>968788.69309</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>801572366.0802745</v>
+        <v>4760418.983088754</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>86712366.08027443</v>
+        <v>90418.9830887545</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>911258753.7968985</v>
+        <v>5638788.69309</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>714860000</v>
+        <v>4670000</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>774860000</v>
+        <v>4670000</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>60000000</v>
+        <v>0</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>26712366.08027444</v>
+        <v>90418.9830887545</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>26712366.08027444</v>
+        <v>90418.9830887545</v>
       </c>
       <c r="K10" t="n">
         <v>0</v>
@@ -725,35 +722,35 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>wCLP</t>
+          <t>wCOP</t>
         </is>
       </c>
       <c r="B11" s="4" t="n">
-        <v>64295100</v>
+        <v>196398753.7968985</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>10230305.18505154</v>
+        <v>801572366.0802745</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>7960305.185051544</v>
+        <v>86712366.08027443</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>66565100</v>
+        <v>911258753.7968985</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>2270000</v>
+        <v>714860000</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>2270000</v>
+        <v>774860000</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>0</v>
+        <v>60000000</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>7960305.185051544</v>
+        <v>26712366.08027444</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>7960305.185051544</v>
+        <v>26712366.08027444</v>
       </c>
       <c r="K11" t="n">
         <v>0</v>
@@ -767,35 +764,35 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>wPEN</t>
+          <t>wCLP</t>
         </is>
       </c>
       <c r="B12" s="4" t="n">
-        <v>122950</v>
+        <v>64295100</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>15770.89</v>
+        <v>10230305.18505154</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>5770.89</v>
+        <v>7960305.185051544</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>132950</v>
+        <v>66565100</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>10000</v>
+        <v>2270000</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>10000</v>
+        <v>2270000</v>
       </c>
       <c r="H12" s="4" t="n">
         <v>0</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>5770.89</v>
+        <v>7960305.185051544</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>5770.89</v>
+        <v>7960305.185051544</v>
       </c>
       <c r="K12" t="n">
         <v>0</v>
@@ -806,41 +803,83 @@
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" s="2" t="inlineStr">
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>wPEN</t>
+        </is>
+      </c>
+      <c r="B13" s="4" t="n">
+        <v>122950</v>
+      </c>
+      <c r="C13" s="4" t="n">
+        <v>15770.89</v>
+      </c>
+      <c r="D13" s="4" t="n">
+        <v>5770.89</v>
+      </c>
+      <c r="E13" s="4" t="n">
+        <v>132950</v>
+      </c>
+      <c r="F13" s="4" t="n">
+        <v>10000</v>
+      </c>
+      <c r="G13" s="4" t="n">
+        <v>10000</v>
+      </c>
+      <c r="H13" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I13" s="4" t="n">
+        <v>5770.89</v>
+      </c>
+      <c r="J13" s="4" t="n">
+        <v>5770.89</v>
+      </c>
+      <c r="K13" t="n">
+        <v>0</v>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>Ethereum, Base, Polygon, Gnosis, BNB Smart Chain, World Chain, Celo</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
         <is>
           <t>Red nueva desde el último cierre: Arc</t>
         </is>
       </c>
-      <c r="E14" s="5" t="inlineStr">
+      <c r="E15" s="5" t="inlineStr">
         <is>
           <t>Bloque de creación 19659303</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>Redes revisadas: Ethereum, Base, Polygon, Gnosis, BNB Smart Chain, World Chain, Celo, HyperEVM, Arc, Arbitrum One, OP Mainnet, Avalanche C-Chain, Unichain, Linea, Scroll, Mantle, Sonic, Monad, Plasma, Ink, Lisk, Sei, Katana, Rootstock</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Para revisar: 9 movimientos (detalle en Emisiones y quemas).</t>
+          <t>Redes revisadas: Ethereum, Base, Polygon, Gnosis, BNB Smart Chain, World Chain, Celo, HyperEVM, Arc, Arbitrum One, OP Mainnet, Avalanche C-Chain, Unichain, Linea, Scroll, Mantle, Sonic, Monad, Plasma, Ink, Lisk, Sei, Katana, Rootstock</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
+          <t>Para revisar: 5 movimientos (detalle en Emisiones y quemas).</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
           <t>La convención horaria no cambia este cierre.</t>
         </is>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
+    <row r="20">
+      <c r="A20" t="inlineStr">
         <is>
           <t>Usa solo datos públicos: las blockchains y las certificaciones publicadas. No calcula el respaldo bancario.</t>
         </is>
@@ -848,15 +887,17 @@
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E14" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E15" r:id="rId1"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
+    <tabColor rgb="007808FE"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
@@ -3613,6 +3654,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
+    <tabColor rgb="007808FE"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
@@ -13418,9 +13460,9 @@
           <t>En tránsito al corte</t>
         </is>
       </c>
-      <c r="M171" t="inlineStr">
-        <is>
-          <t>Salió por el puente el 29/07/2026 hacia Celo y no encontramos la emisión del otro lado (buscada hasta el bloque 78986129 de Celo).</t>
+      <c r="M171" s="6" t="inlineStr">
+        <is>
+          <t>Salió por el puente el 29/07/2026 hacia Celo y no encontramos la emisión del otro lado (buscada hasta el bloque 78988055 de Celo).</t>
         </is>
       </c>
     </row>
@@ -15942,7 +15984,7 @@
         </is>
       </c>
       <c r="K216" t="inlineStr"/>
-      <c r="M216" t="inlineStr">
+      <c r="M216" s="6" t="inlineStr">
         <is>
           <t>Sin clasificar: no tiene evento del puente y quien quema no tiene permiso de emisión.</t>
         </is>
@@ -17104,7 +17146,7 @@
         </is>
       </c>
       <c r="K237" t="inlineStr"/>
-      <c r="M237" t="inlineStr">
+      <c r="M237" s="6" t="inlineStr">
         <is>
           <t>Sin clasificar: no tiene evento del puente y quien quema no tiene permiso de emisión.</t>
         </is>
@@ -20889,9 +20931,9 @@
           <t>En tránsito al corte</t>
         </is>
       </c>
-      <c r="M303" t="inlineStr">
-        <is>
-          <t>Salió por el puente el 02/09/2026 hacia Gnosis y no encontramos la emisión del otro lado (buscada hasta el bloque 48538942 de Gnosis).</t>
+      <c r="M303" s="6" t="inlineStr">
+        <is>
+          <t>Salió por el puente el 02/09/2026 hacia Gnosis y no encontramos la emisión del otro lado (buscada hasta el bloque 48539318 de Gnosis).</t>
         </is>
       </c>
     </row>
@@ -29642,7 +29684,7 @@
       </c>
       <c r="E454" t="inlineStr">
         <is>
-          <t>Sin clasificar</t>
+          <t>Emisión primaria</t>
         </is>
       </c>
       <c r="F454" s="4" t="n">
@@ -29669,7 +29711,7 @@
       <c r="K454" t="inlineStr"/>
       <c r="M454" t="inlineStr">
         <is>
-          <t>Sin clasificar: no tiene evento del puente ni de LimitedMinter.</t>
+          <t>Resuelto por el agente. Verificado: MINTER_ROLE de 0x2b839174fe62466067c22e2a4c8054071f9d8d68 en 0x0dc4f92879b7670e5f4e4e6e3c801d229129d90d al bloque 20356249: sí</t>
         </is>
       </c>
     </row>
@@ -29696,7 +29738,7 @@
       </c>
       <c r="E455" t="inlineStr">
         <is>
-          <t>Sin clasificar</t>
+          <t>Emisión primaria</t>
         </is>
       </c>
       <c r="F455" s="4" t="n">
@@ -29723,7 +29765,7 @@
       <c r="K455" t="inlineStr"/>
       <c r="M455" t="inlineStr">
         <is>
-          <t>Sin clasificar: no tiene evento del puente ni de LimitedMinter.</t>
+          <t>Resuelto por el agente. Verificado: MINTER_ROLE de 0x2b839174fe62466067c22e2a4c8054071f9d8d68 en 0xd76f5faf6888e24d9f04bf92a0c8b921fe4390e0 al bloque 20356249: sí</t>
         </is>
       </c>
     </row>
@@ -30104,7 +30146,7 @@
       </c>
       <c r="E462" t="inlineStr">
         <is>
-          <t>Sin clasificar</t>
+          <t>Emisión primaria</t>
         </is>
       </c>
       <c r="F462" s="4" t="n">
@@ -30131,7 +30173,7 @@
       <c r="K462" t="inlineStr"/>
       <c r="M462" t="inlineStr">
         <is>
-          <t>Sin clasificar: no tiene evento del puente ni de LimitedMinter.</t>
+          <t>Resuelto por el agente. Verificado: MINTER_ROLE de 0x2b839174fe62466067c22e2a4c8054071f9d8d68 en 0xd76f5faf6888e24d9f04bf92a0c8b921fe4390e0 al bloque 20828490: sí</t>
         </is>
       </c>
     </row>
@@ -30158,7 +30200,7 @@
       </c>
       <c r="E463" t="inlineStr">
         <is>
-          <t>Sin clasificar</t>
+          <t>Emisión primaria</t>
         </is>
       </c>
       <c r="F463" s="4" t="n">
@@ -30185,7 +30227,7 @@
       <c r="K463" t="inlineStr"/>
       <c r="M463" t="inlineStr">
         <is>
-          <t>Sin clasificar: no tiene evento del puente ni de LimitedMinter.</t>
+          <t>Resuelto por el agente. Verificado: MINTER_ROLE de 0x2b839174fe62466067c22e2a4c8054071f9d8d68 en 0x0dc4f92879b7670e5f4e4e6e3c801d229129d90d al bloque 20828490: sí</t>
         </is>
       </c>
     </row>
@@ -30300,9 +30342,9 @@
           <t>En tránsito al corte</t>
         </is>
       </c>
-      <c r="M465" t="inlineStr">
-        <is>
-          <t>Salió por el puente el 14/09/2026 hacia Ethereum y no encontramos la emisión del otro lado (buscada hasta el bloque 26099889 de Ethereum).</t>
+      <c r="M465" s="6" t="inlineStr">
+        <is>
+          <t>Salió por el puente el 14/09/2026 hacia Ethereum y no encontramos la emisión del otro lado (buscada hasta el bloque 26100049 de Ethereum).</t>
         </is>
       </c>
     </row>
@@ -40887,6 +40929,7 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
+    <tabColor rgb="007808FE"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
@@ -43923,6 +43966,7 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
+    <tabColor rgb="007808FE"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
@@ -43952,7 +43996,7 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="6" t="inlineStr">
+      <c r="A2" s="7" t="inlineStr">
         <is>
           <t>Las direcciones de los tokens se confirman en cada red leyendo name(), symbol() y decimals() en el contrato.</t>
         </is>
@@ -43962,14 +44006,14 @@
           <t>documentada</t>
         </is>
       </c>
-      <c r="C2" s="6" t="inlineStr">
+      <c r="C2" s="7" t="inlineStr">
         <is>
           <t>CoinGecko (detail_platforms), Blockscout y lectura onchain. Ver config/tokens.yaml.</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="6" t="inlineStr">
+      <c r="A3" s="7" t="inlineStr">
         <is>
           <t>Una emisión es un Transfer desde la dirección cero y una quema es un Transfer hacia la dirección cero.</t>
         </is>
@@ -43979,14 +44023,14 @@
           <t>documentada</t>
         </is>
       </c>
-      <c r="C3" s="6" t="inlineStr">
+      <c r="C3" s="7" t="inlineStr">
         <is>
           <t>Estándar ERC20 de OpenZeppelin y README de github.com/ripio/latam-stables.</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="6" t="inlineStr">
+      <c r="A4" s="7" t="inlineStr">
         <is>
           <t>La conciliación incluye todo movimiento que cambia la cantidad de tokens, también los del puente.</t>
         </is>
@@ -43996,14 +44040,14 @@
           <t>documentada</t>
         </is>
       </c>
-      <c r="C4" s="6" t="inlineStr">
+      <c r="C4" s="7" t="inlineStr">
         <is>
           <t>Saldo de apertura + emisiones − quemas = saldo de cierre, exacto en unidades base, por red.</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="6" t="inlineStr">
+      <c r="A5" s="7" t="inlineStr">
         <is>
           <t>Cada red se calcula por dos caminos independientes: totalSupply() en el bloque del corte y la suma de los movimientos. Si no coinciden, el cierre se detiene.</t>
         </is>
@@ -44013,14 +44057,14 @@
           <t>documentada</t>
         </is>
       </c>
-      <c r="C5" s="6" t="inlineStr">
+      <c r="C5" s="7" t="inlineStr">
         <is>
           <t>Diseño del motor. Una fuente de movimientos se usa solo si concilia exacto.</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="6" t="inlineStr">
+      <c r="A6" s="7" t="inlineStr">
         <is>
           <t>El saldo de apertura es cero solo si el contrato se creó después del corte anterior. El bloque de creación queda como evidencia.</t>
         </is>
@@ -44030,14 +44074,14 @@
           <t>documentada</t>
         </is>
       </c>
-      <c r="C6" s="6" t="inlineStr">
+      <c r="C6" s="7" t="inlineStr">
         <is>
           <t>Bloque de creación por búsqueda en nodo archivo, cruzado con el explorador cuando hay uno.</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="6" t="inlineStr">
+      <c r="A7" s="7" t="inlineStr">
         <is>
           <t>Los movimientos del puente se emparejan por la red de origen, el hash de origen y el número de depósito que trae cada emisión del puente.</t>
         </is>
@@ -44047,14 +44091,14 @@
           <t>documentada</t>
         </is>
       </c>
-      <c r="C7" s="6" t="inlineStr">
+      <c r="C7" s="7" t="inlineStr">
         <is>
           <t>Eventos BridgeDepositInitiated y BridgeMintFulfilled del contrato BridgeDeposit verificado (src/BridgeDeposit.sol).</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="6" t="inlineStr">
+      <c r="A8" s="7" t="inlineStr">
         <is>
           <t>Una emisión es primaria si su transacción tiene el evento Minted del contrato LimitedMinter y ningún evento del puente.</t>
         </is>
@@ -44064,14 +44108,14 @@
           <t>documentada</t>
         </is>
       </c>
-      <c r="C8" s="6" t="inlineStr">
+      <c r="C8" s="7" t="inlineStr">
         <is>
           <t>Contrato LimitedMinter verificado (src/LimitedMinter.sol). Direcciones en config/contracts.yaml.</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="6" t="inlineStr">
+      <c r="A9" s="7" t="inlineStr">
         <is>
           <t>Una quema es rescate primario si quien quema sus propios tokens tiene permiso de emisión (MINTER_ROLE) en el LimitedMinter de esa red, leído en el bloque de la quema.</t>
         </is>
@@ -44081,14 +44125,14 @@
           <t>documentada</t>
         </is>
       </c>
-      <c r="C9" s="6" t="inlineStr">
+      <c r="C9" s="7" t="inlineStr">
         <is>
           <t>Lectura onchain de hasRole(MINTER_ROLE, cuenta) en el LimitedMinter verificado.</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="6" t="inlineStr">
+      <c r="A10" s="7" t="inlineStr">
         <is>
           <t>Lo que no encaja en ninguna de estas reglas queda sin clasificar. No se adivina.</t>
         </is>
@@ -44098,14 +44142,14 @@
           <t>documentada</t>
         </is>
       </c>
-      <c r="C10" s="6" t="inlineStr">
+      <c r="C10" s="7" t="inlineStr">
         <is>
           <t>Regla del motor.</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="6" t="inlineStr">
+      <c r="A11" s="7" t="inlineStr">
         <is>
           <t>La cantidad en circulación es la suma de totalSupply() en las redes revisadas, sin excluir billeteras.</t>
         </is>
@@ -44115,14 +44159,14 @@
           <t>inferida</t>
         </is>
       </c>
-      <c r="C11" s="6" t="inlineStr">
+      <c r="C11" s="7" t="inlineStr">
         <is>
           <t>Reproduce las 9 cifras certificadas publicadas (data/golden/verification.json).</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="6" t="inlineStr">
+      <c r="A12" s="7" t="inlineStr">
         <is>
           <t>La comparación con las cifras certificadas se hace en tokens enteros.</t>
         </is>
@@ -44132,14 +44176,14 @@
           <t>inferida</t>
         </is>
       </c>
-      <c r="C12" s="6" t="inlineStr">
+      <c r="C12" s="7" t="inlineStr">
         <is>
           <t>Regla única para las 9 certificaciones. Decisión de Máximo Sckell.</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="6" t="inlineStr">
+      <c r="A13" s="7" t="inlineStr">
         <is>
           <t>El corte es a las 23:59:59 hora de Buenos Aires del último día del trimestre.</t>
         </is>
@@ -44149,14 +44193,14 @@
           <t>inferida</t>
         </is>
       </c>
-      <c r="C13" s="6" t="inlineStr">
+      <c r="C13" s="7" t="inlineStr">
         <is>
           <t>En los cortes certificados, 23:59:59 de Buenos Aires y de UTC dan el mismo resultado.</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="6" t="inlineStr">
+      <c r="A14" s="7" t="inlineStr">
         <is>
           <t>Las redes revisadas son una lista escrita de redes EVM candidatas, cruzada con CoinGecko y con las redes que nombran los certificados.</t>
         </is>
@@ -44166,14 +44210,14 @@
           <t>documentada</t>
         </is>
       </c>
-      <c r="C14" s="6" t="inlineStr">
+      <c r="C14" s="7" t="inlineStr">
         <is>
           <t>config/chains.yaml, data/discovery.json y data/sources/coingecko_platforms.json.</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="6" t="inlineStr">
+      <c r="A15" s="7" t="inlineStr">
         <is>
           <t>wUYU no se incluye: existe en las mismas redes, pero lo creó una fábrica pública y no hay evidencia de que sea de Ripio.</t>
         </is>
@@ -44183,7 +44227,7 @@
           <t>hipótesis</t>
         </is>
       </c>
-      <c r="C15" s="6" t="inlineStr">
+      <c r="C15" s="7" t="inlineStr">
         <is>
           <t>data/discovery.json</t>
         </is>

--- a/data/closes/2026-09-30/paquete_cierre_2026-09-30.xlsx
+++ b/data/closes/2026-09-30/paquete_cierre_2026-09-30.xlsx
@@ -520,7 +520,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Corte: 30/09/2026 23:59:59 hora de Buenos Aires. Cierre anterior: 30/06/2026. Generado: 2026-10-01T21:07:02+00:00 (UTC).</t>
+          <t>Corte: 30/09/2026 23:59:59 hora de Buenos Aires. Cierre anterior: 30/06/2026. Generado: 2026-10-01T22:04:51+00:00 (UTC).</t>
         </is>
       </c>
     </row>
@@ -1024,7 +1024,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>rpc:mainnet.gateway.tenderly.co</t>
+          <t>blockscout:https://eth.blockscout.com/api</t>
         </is>
       </c>
     </row>
@@ -1120,7 +1120,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>rpc:polygon.gateway.tenderly.co</t>
+          <t>blockscout:https://polygon.blockscout.com/api</t>
         </is>
       </c>
     </row>
@@ -1264,7 +1264,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>rpc:worldchain-mainnet.gateway.tenderly.co</t>
+          <t>blockscout:https://worldchain-mainnet.explorer.alchemy.com/api</t>
         </is>
       </c>
     </row>
@@ -1312,7 +1312,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>rpc:celo.gateway.tenderly.co</t>
+          <t>blockscout:https://celo.blockscout.com/api</t>
         </is>
       </c>
     </row>
@@ -1458,7 +1458,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>rpc:mainnet.gateway.tenderly.co</t>
+          <t>blockscout:https://eth.blockscout.com/api</t>
         </is>
       </c>
     </row>
@@ -1554,7 +1554,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>rpc:polygon.gateway.tenderly.co</t>
+          <t>blockscout:https://polygon.blockscout.com/api</t>
         </is>
       </c>
     </row>
@@ -1698,7 +1698,7 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>rpc:worldchain-mainnet.gateway.tenderly.co</t>
+          <t>blockscout:https://worldchain-mainnet.explorer.alchemy.com/api</t>
         </is>
       </c>
     </row>
@@ -1746,7 +1746,7 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>rpc:celo.gateway.tenderly.co</t>
+          <t>blockscout:https://celo.blockscout.com/api</t>
         </is>
       </c>
     </row>
@@ -1892,7 +1892,7 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>rpc:mainnet.gateway.tenderly.co</t>
+          <t>blockscout:https://eth.blockscout.com/api</t>
         </is>
       </c>
     </row>
@@ -1988,7 +1988,7 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>rpc:polygon.gateway.tenderly.co</t>
+          <t>blockscout:https://polygon.blockscout.com/api</t>
         </is>
       </c>
     </row>
@@ -2132,7 +2132,7 @@
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>rpc:worldchain-mainnet.gateway.tenderly.co</t>
+          <t>blockscout:https://worldchain-mainnet.explorer.alchemy.com/api</t>
         </is>
       </c>
     </row>
@@ -2180,7 +2180,7 @@
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>rpc:celo.gateway.tenderly.co</t>
+          <t>blockscout:https://celo.blockscout.com/api</t>
         </is>
       </c>
     </row>
@@ -2326,7 +2326,7 @@
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>rpc:mainnet.gateway.tenderly.co</t>
+          <t>blockscout:https://eth.blockscout.com/api</t>
         </is>
       </c>
     </row>
@@ -2422,7 +2422,7 @@
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>rpc:polygon.gateway.tenderly.co</t>
+          <t>blockscout:https://polygon.blockscout.com/api</t>
         </is>
       </c>
     </row>
@@ -2566,7 +2566,7 @@
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>rpc:worldchain-mainnet.gateway.tenderly.co</t>
+          <t>blockscout:https://worldchain-mainnet.explorer.alchemy.com/api</t>
         </is>
       </c>
     </row>
@@ -2614,7 +2614,7 @@
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>rpc:celo.gateway.tenderly.co</t>
+          <t>blockscout:https://celo.blockscout.com/api</t>
         </is>
       </c>
     </row>
@@ -2760,7 +2760,7 @@
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>rpc:mainnet.gateway.tenderly.co</t>
+          <t>blockscout:https://eth.blockscout.com/api</t>
         </is>
       </c>
     </row>
@@ -2856,7 +2856,7 @@
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>rpc:polygon.gateway.tenderly.co</t>
+          <t>blockscout:https://polygon.blockscout.com/api</t>
         </is>
       </c>
     </row>
@@ -3000,7 +3000,7 @@
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>rpc:worldchain-mainnet.gateway.tenderly.co</t>
+          <t>blockscout:https://worldchain-mainnet.explorer.alchemy.com/api</t>
         </is>
       </c>
     </row>
@@ -3048,7 +3048,7 @@
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>rpc:celo.gateway.tenderly.co</t>
+          <t>blockscout:https://celo.blockscout.com/api</t>
         </is>
       </c>
     </row>
@@ -3194,7 +3194,7 @@
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>rpc:mainnet.gateway.tenderly.co</t>
+          <t>blockscout:https://eth.blockscout.com/api</t>
         </is>
       </c>
     </row>
@@ -3290,7 +3290,7 @@
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>rpc:polygon.gateway.tenderly.co</t>
+          <t>blockscout:https://polygon.blockscout.com/api</t>
         </is>
       </c>
     </row>
@@ -3434,7 +3434,7 @@
       </c>
       <c r="L52" t="inlineStr">
         <is>
-          <t>rpc:worldchain-mainnet.gateway.tenderly.co</t>
+          <t>blockscout:https://worldchain-mainnet.explorer.alchemy.com/api</t>
         </is>
       </c>
     </row>
@@ -3482,7 +3482,7 @@
       </c>
       <c r="L53" t="inlineStr">
         <is>
-          <t>rpc:celo.gateway.tenderly.co</t>
+          <t>blockscout:https://celo.blockscout.com/api</t>
         </is>
       </c>
     </row>
@@ -13462,7 +13462,7 @@
       </c>
       <c r="M171" s="6" t="inlineStr">
         <is>
-          <t>Salió por el puente el 29/07/2026 hacia Celo y no encontramos la emisión del otro lado (buscada hasta el bloque 78988055 de Celo).</t>
+          <t>Salió por el puente el 29/07/2026 hacia Celo y no encontramos la emisión del otro lado (buscada hasta el bloque 78991528 de Celo).</t>
         </is>
       </c>
     </row>
@@ -20933,7 +20933,7 @@
       </c>
       <c r="M303" s="6" t="inlineStr">
         <is>
-          <t>Salió por el puente el 02/09/2026 hacia Gnosis y no encontramos la emisión del otro lado (buscada hasta el bloque 48539318 de Gnosis).</t>
+          <t>Salió por el puente el 02/09/2026 hacia Gnosis y no encontramos la emisión del otro lado (buscada hasta el bloque 48540003 de Gnosis).</t>
         </is>
       </c>
     </row>
@@ -30344,7 +30344,7 @@
       </c>
       <c r="M465" s="6" t="inlineStr">
         <is>
-          <t>Salió por el puente el 14/09/2026 hacia Ethereum y no encontramos la emisión del otro lado (buscada hasta el bloque 26100049 de Ethereum).</t>
+          <t>Salió por el puente el 14/09/2026 hacia Ethereum y no encontramos la emisión del otro lado (buscada hasta el bloque 26100337 de Ethereum).</t>
         </is>
       </c>
     </row>
@@ -41059,10 +41059,14 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
+          <t>blockscout:https://eth.blockscout.com/api</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
           <t>rpc:mainnet.gateway.tenderly.co</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
     </row>
     <row r="3">
@@ -41171,10 +41175,14 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
+          <t>blockscout:https://polygon.blockscout.com/api</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
           <t>rpc:polygon.gateway.tenderly.co</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
     </row>
     <row r="5">
@@ -41333,10 +41341,14 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
+          <t>blockscout:https://worldchain-mainnet.explorer.alchemy.com/api</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
           <t>rpc:worldchain-mainnet.gateway.tenderly.co</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
     </row>
     <row r="8">
@@ -41387,10 +41399,14 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
+          <t>blockscout:https://celo.blockscout.com/api</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
           <t>rpc:celo.gateway.tenderly.co</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
     </row>
     <row r="9">
@@ -41549,10 +41565,14 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
+          <t>blockscout:https://eth.blockscout.com/api</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
           <t>rpc:mainnet.gateway.tenderly.co</t>
         </is>
       </c>
-      <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr"/>
     </row>
     <row r="12">
@@ -41661,10 +41681,14 @@
       </c>
       <c r="J13" t="inlineStr">
         <is>
+          <t>blockscout:https://polygon.blockscout.com/api</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
           <t>rpc:polygon.gateway.tenderly.co</t>
         </is>
       </c>
-      <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr"/>
     </row>
     <row r="14">
@@ -41823,10 +41847,14 @@
       </c>
       <c r="J16" t="inlineStr">
         <is>
+          <t>blockscout:https://worldchain-mainnet.explorer.alchemy.com/api</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
           <t>rpc:worldchain-mainnet.gateway.tenderly.co</t>
         </is>
       </c>
-      <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr"/>
     </row>
     <row r="17">
@@ -41877,10 +41905,14 @@
       </c>
       <c r="J17" t="inlineStr">
         <is>
+          <t>blockscout:https://celo.blockscout.com/api</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
           <t>rpc:celo.gateway.tenderly.co</t>
         </is>
       </c>
-      <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr"/>
     </row>
     <row r="18">
@@ -42039,10 +42071,14 @@
       </c>
       <c r="J20" t="inlineStr">
         <is>
+          <t>blockscout:https://eth.blockscout.com/api</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
           <t>rpc:mainnet.gateway.tenderly.co</t>
         </is>
       </c>
-      <c r="K20" t="inlineStr"/>
       <c r="L20" t="inlineStr"/>
     </row>
     <row r="21">
@@ -42151,10 +42187,14 @@
       </c>
       <c r="J22" t="inlineStr">
         <is>
+          <t>blockscout:https://polygon.blockscout.com/api</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
           <t>rpc:polygon.gateway.tenderly.co</t>
         </is>
       </c>
-      <c r="K22" t="inlineStr"/>
       <c r="L22" t="inlineStr"/>
     </row>
     <row r="23">
@@ -42313,10 +42353,14 @@
       </c>
       <c r="J25" t="inlineStr">
         <is>
+          <t>blockscout:https://worldchain-mainnet.explorer.alchemy.com/api</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
           <t>rpc:worldchain-mainnet.gateway.tenderly.co</t>
         </is>
       </c>
-      <c r="K25" t="inlineStr"/>
       <c r="L25" t="inlineStr"/>
     </row>
     <row r="26">
@@ -42367,10 +42411,14 @@
       </c>
       <c r="J26" t="inlineStr">
         <is>
+          <t>blockscout:https://celo.blockscout.com/api</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
           <t>rpc:celo.gateway.tenderly.co</t>
         </is>
       </c>
-      <c r="K26" t="inlineStr"/>
       <c r="L26" t="inlineStr"/>
     </row>
     <row r="27">
@@ -42529,10 +42577,14 @@
       </c>
       <c r="J29" t="inlineStr">
         <is>
+          <t>blockscout:https://eth.blockscout.com/api</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
           <t>rpc:mainnet.gateway.tenderly.co</t>
         </is>
       </c>
-      <c r="K29" t="inlineStr"/>
       <c r="L29" t="inlineStr"/>
     </row>
     <row r="30">
@@ -42641,10 +42693,14 @@
       </c>
       <c r="J31" t="inlineStr">
         <is>
+          <t>blockscout:https://polygon.blockscout.com/api</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
           <t>rpc:polygon.gateway.tenderly.co</t>
         </is>
       </c>
-      <c r="K31" t="inlineStr"/>
       <c r="L31" t="inlineStr"/>
     </row>
     <row r="32">
@@ -42803,10 +42859,14 @@
       </c>
       <c r="J34" t="inlineStr">
         <is>
+          <t>blockscout:https://worldchain-mainnet.explorer.alchemy.com/api</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
           <t>rpc:worldchain-mainnet.gateway.tenderly.co</t>
         </is>
       </c>
-      <c r="K34" t="inlineStr"/>
       <c r="L34" t="inlineStr"/>
     </row>
     <row r="35">
@@ -42857,10 +42917,14 @@
       </c>
       <c r="J35" t="inlineStr">
         <is>
+          <t>blockscout:https://celo.blockscout.com/api</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
           <t>rpc:celo.gateway.tenderly.co</t>
         </is>
       </c>
-      <c r="K35" t="inlineStr"/>
       <c r="L35" t="inlineStr"/>
     </row>
     <row r="36">
@@ -43019,10 +43083,14 @@
       </c>
       <c r="J38" t="inlineStr">
         <is>
+          <t>blockscout:https://eth.blockscout.com/api</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
           <t>rpc:mainnet.gateway.tenderly.co</t>
         </is>
       </c>
-      <c r="K38" t="inlineStr"/>
       <c r="L38" t="inlineStr"/>
     </row>
     <row r="39">
@@ -43131,10 +43199,14 @@
       </c>
       <c r="J40" t="inlineStr">
         <is>
+          <t>blockscout:https://polygon.blockscout.com/api</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
           <t>rpc:polygon.gateway.tenderly.co</t>
         </is>
       </c>
-      <c r="K40" t="inlineStr"/>
       <c r="L40" t="inlineStr"/>
     </row>
     <row r="41">
@@ -43293,10 +43365,14 @@
       </c>
       <c r="J43" t="inlineStr">
         <is>
+          <t>blockscout:https://worldchain-mainnet.explorer.alchemy.com/api</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
           <t>rpc:worldchain-mainnet.gateway.tenderly.co</t>
         </is>
       </c>
-      <c r="K43" t="inlineStr"/>
       <c r="L43" t="inlineStr"/>
     </row>
     <row r="44">
@@ -43347,10 +43423,14 @@
       </c>
       <c r="J44" t="inlineStr">
         <is>
+          <t>blockscout:https://celo.blockscout.com/api</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
           <t>rpc:celo.gateway.tenderly.co</t>
         </is>
       </c>
-      <c r="K44" t="inlineStr"/>
       <c r="L44" t="inlineStr"/>
     </row>
     <row r="45">
@@ -43509,10 +43589,14 @@
       </c>
       <c r="J47" t="inlineStr">
         <is>
+          <t>blockscout:https://eth.blockscout.com/api</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
           <t>rpc:mainnet.gateway.tenderly.co</t>
         </is>
       </c>
-      <c r="K47" t="inlineStr"/>
       <c r="L47" t="inlineStr"/>
     </row>
     <row r="48">
@@ -43621,10 +43705,14 @@
       </c>
       <c r="J49" t="inlineStr">
         <is>
+          <t>blockscout:https://polygon.blockscout.com/api</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
           <t>rpc:polygon.gateway.tenderly.co</t>
         </is>
       </c>
-      <c r="K49" t="inlineStr"/>
       <c r="L49" t="inlineStr"/>
     </row>
     <row r="50">
@@ -43783,10 +43871,14 @@
       </c>
       <c r="J52" t="inlineStr">
         <is>
+          <t>blockscout:https://worldchain-mainnet.explorer.alchemy.com/api</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
           <t>rpc:worldchain-mainnet.gateway.tenderly.co</t>
         </is>
       </c>
-      <c r="K52" t="inlineStr"/>
       <c r="L52" t="inlineStr"/>
     </row>
     <row r="53">
@@ -43837,10 +43929,14 @@
       </c>
       <c r="J53" t="inlineStr">
         <is>
+          <t>blockscout:https://celo.blockscout.com/api</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
           <t>rpc:celo.gateway.tenderly.co</t>
         </is>
       </c>
-      <c r="K53" t="inlineStr"/>
       <c r="L53" t="inlineStr"/>
     </row>
     <row r="54">

--- a/data/closes/2026-09-30/paquete_cierre_2026-09-30.xlsx
+++ b/data/closes/2026-09-30/paquete_cierre_2026-09-30.xlsx
@@ -520,7 +520,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Corte: 30/09/2026 23:59:59 hora de Buenos Aires. Cierre anterior: 30/06/2026. Generado: 2026-10-01T22:04:51+00:00 (UTC).</t>
+          <t>Corte: 30/09/2026 23:59:59 hora de Buenos Aires. Cierre anterior: 30/06/2026. Generado: 2026-10-02T01:36:10+00:00 (UTC).</t>
         </is>
       </c>
     </row>
@@ -13462,7 +13462,7 @@
       </c>
       <c r="M171" s="6" t="inlineStr">
         <is>
-          <t>Salió por el puente el 29/07/2026 hacia Celo y no encontramos la emisión del otro lado (buscada hasta el bloque 78991528 de Celo).</t>
+          <t>Salió por el puente el 29/07/2026 hacia Celo y no encontramos la emisión del otro lado (buscada hasta el bloque 79004207 de Celo).</t>
         </is>
       </c>
     </row>
@@ -20933,7 +20933,7 @@
       </c>
       <c r="M303" s="6" t="inlineStr">
         <is>
-          <t>Salió por el puente el 02/09/2026 hacia Gnosis y no encontramos la emisión del otro lado (buscada hasta el bloque 48540003 de Gnosis).</t>
+          <t>Salió por el puente el 02/09/2026 hacia Gnosis y no encontramos la emisión del otro lado (buscada hasta el bloque 48542497 de Gnosis).</t>
         </is>
       </c>
     </row>
@@ -30344,7 +30344,7 @@
       </c>
       <c r="M465" s="6" t="inlineStr">
         <is>
-          <t>Salió por el puente el 14/09/2026 hacia Ethereum y no encontramos la emisión del otro lado (buscada hasta el bloque 26100337 de Ethereum).</t>
+          <t>Salió por el puente el 14/09/2026 hacia Ethereum y no encontramos la emisión del otro lado (buscada hasta el bloque 26101390 de Ethereum).</t>
         </is>
       </c>
     </row>

--- a/data/closes/2026-09-30/paquete_cierre_2026-09-30.xlsx
+++ b/data/closes/2026-09-30/paquete_cierre_2026-09-30.xlsx
@@ -520,7 +520,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Corte: 30/09/2026 23:59:59 hora de Buenos Aires. Cierre anterior: 30/06/2026. Generado: 2026-10-02T01:36:10+00:00 (UTC).</t>
+          <t>Corte: 30/09/2026 23:59:59 hora de Buenos Aires. Cierre anterior: 30/06/2026. Generado: 2026-10-02T02:10:35+00:00 (UTC).</t>
         </is>
       </c>
     </row>
@@ -13462,7 +13462,7 @@
       </c>
       <c r="M171" s="6" t="inlineStr">
         <is>
-          <t>Salió por el puente el 29/07/2026 hacia Celo y no encontramos la emisión del otro lado (buscada hasta el bloque 79004207 de Celo).</t>
+          <t>Salió por el puente el 29/07/2026 hacia Celo y no encontramos la emisión del otro lado (buscada hasta el bloque 79006268 de Celo).</t>
         </is>
       </c>
     </row>
@@ -20933,7 +20933,7 @@
       </c>
       <c r="M303" s="6" t="inlineStr">
         <is>
-          <t>Salió por el puente el 02/09/2026 hacia Gnosis y no encontramos la emisión del otro lado (buscada hasta el bloque 48542497 de Gnosis).</t>
+          <t>Salió por el puente el 02/09/2026 hacia Gnosis y no encontramos la emisión del otro lado (buscada hasta el bloque 48542905 de Gnosis).</t>
         </is>
       </c>
     </row>
@@ -30344,7 +30344,7 @@
       </c>
       <c r="M465" s="6" t="inlineStr">
         <is>
-          <t>Salió por el puente el 14/09/2026 hacia Ethereum y no encontramos la emisión del otro lado (buscada hasta el bloque 26101390 de Ethereum).</t>
+          <t>Salió por el puente el 14/09/2026 hacia Ethereum y no encontramos la emisión del otro lado (buscada hasta el bloque 26101562 de Ethereum).</t>
         </is>
       </c>
     </row>

--- a/data/closes/2026-09-30/paquete_cierre_2026-09-30.xlsx
+++ b/data/closes/2026-09-30/paquete_cierre_2026-09-30.xlsx
@@ -520,7 +520,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Corte: 30/09/2026 23:59:59 hora de Buenos Aires. Cierre anterior: 30/06/2026. Generado: 2026-10-02T02:10:35+00:00 (UTC).</t>
+          <t>Corte: 30/09/2026 23:59:59 hora de Buenos Aires. Cierre anterior: 30/06/2026. Generado: 2026-10-02T19:37:33+00:00 (UTC).</t>
         </is>
       </c>
     </row>
@@ -13462,7 +13462,7 @@
       </c>
       <c r="M171" s="6" t="inlineStr">
         <is>
-          <t>Salió por el puente el 29/07/2026 hacia Celo y no encontramos la emisión del otro lado (buscada hasta el bloque 79006268 de Celo).</t>
+          <t>Salió por el puente el 29/07/2026 hacia Celo y no encontramos la emisión del otro lado (buscada hasta el bloque 79069091 de Celo).</t>
         </is>
       </c>
     </row>
@@ -20933,7 +20933,7 @@
       </c>
       <c r="M303" s="6" t="inlineStr">
         <is>
-          <t>Salió por el puente el 02/09/2026 hacia Gnosis y no encontramos la emisión del otro lado (buscada hasta el bloque 48542905 de Gnosis).</t>
+          <t>Salió por el puente el 02/09/2026 hacia Gnosis y no encontramos la emisión del otro lado (buscada hasta el bloque 48555205 de Gnosis).</t>
         </is>
       </c>
     </row>
@@ -30344,7 +30344,7 @@
       </c>
       <c r="M465" s="6" t="inlineStr">
         <is>
-          <t>Salió por el puente el 14/09/2026 hacia Ethereum y no encontramos la emisión del otro lado (buscada hasta el bloque 26101562 de Ethereum).</t>
+          <t>Salió por el puente el 14/09/2026 hacia Ethereum y no encontramos la emisión del otro lado (buscada hasta el bloque 26106772 de Ethereum).</t>
         </is>
       </c>
     </row>

--- a/data/closes/2026-09-30/paquete_cierre_2026-09-30.xlsx
+++ b/data/closes/2026-09-30/paquete_cierre_2026-09-30.xlsx
@@ -485,7 +485,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A2:L20"/>
+  <dimension ref="A2:L22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -520,7 +520,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Corte: 30/09/2026 23:59:59 hora de Buenos Aires. Cierre anterior: 30/06/2026. Generado: 2026-10-02T19:37:33+00:00 (UTC).</t>
+          <t>Corte: 30/09/2026 23:59:59 hora de Buenos Aires. Cierre anterior: 30/06/2026. Generado: 2026-10-03T18:09:23+00:00 (UTC).</t>
         </is>
       </c>
     </row>
@@ -531,6 +531,13 @@
         </is>
       </c>
     </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Alcance: 54 de 54 pares token y red conciliados.</t>
+        </is>
+      </c>
+    </row>
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
@@ -878,8 +885,22 @@
         </is>
       </c>
     </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Verificado contra la blockchain: en cada red, la cantidad de tokens al corte coincide exacto, al último decimal, con la apertura más las emisiones menos las quemas.</t>
+        </is>
+      </c>
+    </row>
     <row r="20">
       <c r="A20" t="inlineStr">
+        <is>
+          <t>Control extra: una segunda fuente independiente confirmó cada movimiento en 40 de 54 pares. En el resto no hay una segunda fuente gratuita disponible y completa.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
         <is>
           <t>Usa solo datos públicos: las blockchains y las certificaciones publicadas. No calcula el respaldo bancario.</t>
         </is>
@@ -1360,7 +1381,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>rpc:hyperliquid-json-rpc.stakely.io,rpc.hypurrscan.io</t>
+          <t>etherscan:https://api.etherscan.io/v2/api</t>
         </is>
       </c>
     </row>
@@ -1794,7 +1815,7 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>rpc:hyperliquid-json-rpc.stakely.io,rpc.hypurrscan.io</t>
+          <t>etherscan:https://api.etherscan.io/v2/api</t>
         </is>
       </c>
     </row>
@@ -2228,7 +2249,7 @@
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>rpc:hyperliquid-json-rpc.stakely.io,rpc.hypurrscan.io</t>
+          <t>etherscan:https://api.etherscan.io/v2/api</t>
         </is>
       </c>
     </row>
@@ -2662,7 +2683,7 @@
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>rpc:hyperliquid-json-rpc.stakely.io,rpc.hypurrscan.io</t>
+          <t>etherscan:https://api.etherscan.io/v2/api</t>
         </is>
       </c>
     </row>
@@ -3096,7 +3117,7 @@
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>rpc:hyperliquid-json-rpc.stakely.io,rpc.hypurrscan.io</t>
+          <t>etherscan:https://api.etherscan.io/v2/api</t>
         </is>
       </c>
     </row>
@@ -3530,7 +3551,7 @@
       </c>
       <c r="L54" t="inlineStr">
         <is>
-          <t>rpc:hyperliquid-json-rpc.stakely.io,rpc.hypurrscan.io</t>
+          <t>etherscan:https://api.etherscan.io/v2/api</t>
         </is>
       </c>
     </row>
@@ -13462,7 +13483,7 @@
       </c>
       <c r="M171" s="6" t="inlineStr">
         <is>
-          <t>Salió por el puente el 29/07/2026 hacia Celo y no encontramos la emisión del otro lado (buscada hasta el bloque 79069091 de Celo).</t>
+          <t>Salió por el puente el 29/07/2026 hacia Celo y no encontramos la emisión del otro lado (buscada hasta el bloque 79150197 de Celo).</t>
         </is>
       </c>
     </row>
@@ -20933,7 +20954,7 @@
       </c>
       <c r="M303" s="6" t="inlineStr">
         <is>
-          <t>Salió por el puente el 02/09/2026 hacia Gnosis y no encontramos la emisión del otro lado (buscada hasta el bloque 48555205 de Gnosis).</t>
+          <t>Salió por el puente el 02/09/2026 hacia Gnosis y no encontramos la emisión del otro lado (buscada hasta el bloque 48571094 de Gnosis).</t>
         </is>
       </c>
     </row>
@@ -30344,7 +30365,7 @@
       </c>
       <c r="M465" s="6" t="inlineStr">
         <is>
-          <t>Salió por el puente el 14/09/2026 hacia Ethereum y no encontramos la emisión del otro lado (buscada hasta el bloque 26106772 de Ethereum).</t>
+          <t>Salió por el puente el 14/09/2026 hacia Ethereum y no encontramos la emisión del otro lado (buscada hasta el bloque 26113511 de Ethereum).</t>
         </is>
       </c>
     </row>
@@ -40933,7 +40954,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L57"/>
+  <dimension ref="A1:N57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -40948,6 +40969,8 @@
     <col width="40" customWidth="1" min="10" max="10"/>
     <col width="30" customWidth="1" min="11" max="11"/>
     <col width="30" customWidth="1" min="12" max="12"/>
+    <col width="24" customWidth="1" min="13" max="13"/>
+    <col width="60" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -41010,6 +41033,16 @@
           <t>Fuentes incompletas</t>
         </is>
       </c>
+      <c r="M1" s="3" t="inlineStr">
+        <is>
+          <t>Segunda fuente</t>
+        </is>
+      </c>
+      <c r="N1" s="3" t="inlineStr">
+        <is>
+          <t>Detalle de la segunda fuente</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -41068,6 +41101,16 @@
         </is>
       </c>
       <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>confirmado por una segunda fuente</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>Coinciden eth.blockscout.com y mainnet.gateway.tenderly.co.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -41126,6 +41169,16 @@
           <t>blockscout:https://base.blockscout.com/api</t>
         </is>
       </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>una sola fuente</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>Una sola fuente: base.blockscout.com devolvió una lista incompleta.</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -41184,6 +41237,16 @@
         </is>
       </c>
       <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>confirmado por una segunda fuente</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>Coinciden polygon.blockscout.com y polygon.gateway.tenderly.co.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -41238,6 +41301,16 @@
       </c>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>una sola fuente</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>Una sola fuente: no hay una segunda fuente gratuita para esta red.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -41290,8 +41363,22 @@
           <t>bscscan list + RPC receipts</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr"/>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>rpc:bsc-mainnet.nodereal.io/v1/***</t>
+        </is>
+      </c>
       <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>confirmado por una segunda fuente</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>Coinciden bscscan list + RPC receipts y bsc-mainnet.nodereal.io.</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -41350,6 +41437,16 @@
         </is>
       </c>
       <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>confirmado por una segunda fuente</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>Coinciden worldchain-mainnet.explorer.alchemy.com y worldchain-mainnet.gateway.tenderly.co.</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -41408,6 +41505,16 @@
         </is>
       </c>
       <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>confirmado por una segunda fuente</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>Coinciden celo.blockscout.com y celo.gateway.tenderly.co.</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -41457,11 +41564,25 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
+          <t>etherscan:https://api.etherscan.io/v2/api</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
           <t>rpc:hyperliquid-json-rpc.stakely.io,rpc.hypurrscan.io</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>confirmado por una segunda fuente</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>Coinciden api.etherscan.io y hyperliquid-json-rpc.stakely.io,rpc.hypurrscan.io.</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -41516,6 +41637,16 @@
       </c>
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>una sola fuente</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>Una sola fuente: no hay una segunda fuente gratuita para esta red.</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -41574,6 +41705,16 @@
         </is>
       </c>
       <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>confirmado por una segunda fuente</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>Coinciden eth.blockscout.com y mainnet.gateway.tenderly.co.</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -41632,6 +41773,16 @@
         </is>
       </c>
       <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>confirmado por una segunda fuente</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>Coinciden base.blockscout.com y mainnet.base.org.</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -41690,6 +41841,16 @@
         </is>
       </c>
       <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>confirmado por una segunda fuente</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>Coinciden polygon.blockscout.com y polygon.gateway.tenderly.co.</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -41744,6 +41905,16 @@
       </c>
       <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>una sola fuente</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>Una sola fuente: no hay una segunda fuente gratuita para esta red.</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -41796,8 +41967,22 @@
           <t>bscscan list + RPC receipts</t>
         </is>
       </c>
-      <c r="K15" t="inlineStr"/>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>rpc:bsc-mainnet.nodereal.io/v1/***</t>
+        </is>
+      </c>
       <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>confirmado por una segunda fuente</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>Coinciden bscscan list + RPC receipts y bsc-mainnet.nodereal.io.</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -41856,6 +42041,16 @@
         </is>
       </c>
       <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>confirmado por una segunda fuente</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>Coinciden worldchain-mainnet.explorer.alchemy.com y worldchain-mainnet.gateway.tenderly.co.</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -41914,6 +42109,16 @@
         </is>
       </c>
       <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>confirmado por una segunda fuente</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>Coinciden celo.blockscout.com y celo.gateway.tenderly.co.</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -41963,11 +42168,25 @@
       </c>
       <c r="J18" t="inlineStr">
         <is>
+          <t>etherscan:https://api.etherscan.io/v2/api</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
           <t>rpc:hyperliquid-json-rpc.stakely.io,rpc.hypurrscan.io</t>
         </is>
       </c>
-      <c r="K18" t="inlineStr"/>
       <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>confirmado por una segunda fuente</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>Coinciden api.etherscan.io y hyperliquid-json-rpc.stakely.io,rpc.hypurrscan.io.</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -42022,6 +42241,16 @@
       </c>
       <c r="K19" t="inlineStr"/>
       <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>una sola fuente</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>Una sola fuente: no hay una segunda fuente gratuita para esta red.</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -42080,6 +42309,16 @@
         </is>
       </c>
       <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>confirmado por una segunda fuente</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>Coinciden eth.blockscout.com y mainnet.gateway.tenderly.co.</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -42138,6 +42377,16 @@
         </is>
       </c>
       <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>confirmado por una segunda fuente</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>Coinciden base.blockscout.com y mainnet.base.org.</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -42196,6 +42445,16 @@
         </is>
       </c>
       <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>confirmado por una segunda fuente</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>Coinciden polygon.blockscout.com y polygon.gateway.tenderly.co.</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -42250,6 +42509,16 @@
       </c>
       <c r="K23" t="inlineStr"/>
       <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>una sola fuente</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>Una sola fuente: no hay una segunda fuente gratuita para esta red.</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -42302,8 +42571,22 @@
           <t>bscscan list + RPC receipts</t>
         </is>
       </c>
-      <c r="K24" t="inlineStr"/>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>rpc:bsc-mainnet.nodereal.io/v1/***</t>
+        </is>
+      </c>
       <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>confirmado por una segunda fuente</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>Coinciden bscscan list + RPC receipts y bsc-mainnet.nodereal.io.</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -42362,6 +42645,16 @@
         </is>
       </c>
       <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>confirmado por una segunda fuente</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>Coinciden worldchain-mainnet.explorer.alchemy.com y worldchain-mainnet.gateway.tenderly.co.</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -42420,6 +42713,16 @@
         </is>
       </c>
       <c r="L26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>confirmado por una segunda fuente</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>Coinciden celo.blockscout.com y celo.gateway.tenderly.co.</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -42469,11 +42772,25 @@
       </c>
       <c r="J27" t="inlineStr">
         <is>
+          <t>etherscan:https://api.etherscan.io/v2/api</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
           <t>rpc:hyperliquid-json-rpc.stakely.io,rpc.hypurrscan.io</t>
         </is>
       </c>
-      <c r="K27" t="inlineStr"/>
       <c r="L27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>confirmado por una segunda fuente</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>Coinciden api.etherscan.io y hyperliquid-json-rpc.stakely.io,rpc.hypurrscan.io.</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -42528,6 +42845,16 @@
       </c>
       <c r="K28" t="inlineStr"/>
       <c r="L28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>una sola fuente</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>Una sola fuente: no hay una segunda fuente gratuita para esta red.</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -42586,6 +42913,16 @@
         </is>
       </c>
       <c r="L29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>confirmado por una segunda fuente</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>Coinciden eth.blockscout.com y mainnet.gateway.tenderly.co.</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -42644,6 +42981,16 @@
         </is>
       </c>
       <c r="L30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>confirmado por una segunda fuente</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>Coinciden base.blockscout.com y mainnet.base.org.</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -42702,6 +43049,16 @@
         </is>
       </c>
       <c r="L31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>confirmado por una segunda fuente</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>Coinciden polygon.blockscout.com y polygon.gateway.tenderly.co.</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -42756,6 +43113,16 @@
       </c>
       <c r="K32" t="inlineStr"/>
       <c r="L32" t="inlineStr"/>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>una sola fuente</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr">
+        <is>
+          <t>Una sola fuente: no hay una segunda fuente gratuita para esta red.</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -42808,8 +43175,22 @@
           <t>bscscan list + RPC receipts</t>
         </is>
       </c>
-      <c r="K33" t="inlineStr"/>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>rpc:bsc-mainnet.nodereal.io/v1/***</t>
+        </is>
+      </c>
       <c r="L33" t="inlineStr"/>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>confirmado por una segunda fuente</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr">
+        <is>
+          <t>Coinciden bscscan list + RPC receipts y bsc-mainnet.nodereal.io.</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -42868,6 +43249,16 @@
         </is>
       </c>
       <c r="L34" t="inlineStr"/>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>confirmado por una segunda fuente</t>
+        </is>
+      </c>
+      <c r="N34" t="inlineStr">
+        <is>
+          <t>Coinciden worldchain-mainnet.explorer.alchemy.com y worldchain-mainnet.gateway.tenderly.co.</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -42926,6 +43317,16 @@
         </is>
       </c>
       <c r="L35" t="inlineStr"/>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>confirmado por una segunda fuente</t>
+        </is>
+      </c>
+      <c r="N35" t="inlineStr">
+        <is>
+          <t>Coinciden celo.blockscout.com y celo.gateway.tenderly.co.</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -42975,11 +43376,25 @@
       </c>
       <c r="J36" t="inlineStr">
         <is>
+          <t>etherscan:https://api.etherscan.io/v2/api</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
           <t>rpc:hyperliquid-json-rpc.stakely.io,rpc.hypurrscan.io</t>
         </is>
       </c>
-      <c r="K36" t="inlineStr"/>
       <c r="L36" t="inlineStr"/>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>confirmado por una segunda fuente</t>
+        </is>
+      </c>
+      <c r="N36" t="inlineStr">
+        <is>
+          <t>Coinciden api.etherscan.io y hyperliquid-json-rpc.stakely.io,rpc.hypurrscan.io.</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -43034,6 +43449,16 @@
       </c>
       <c r="K37" t="inlineStr"/>
       <c r="L37" t="inlineStr"/>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>una sola fuente</t>
+        </is>
+      </c>
+      <c r="N37" t="inlineStr">
+        <is>
+          <t>Una sola fuente: no hay una segunda fuente gratuita para esta red.</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -43092,6 +43517,16 @@
         </is>
       </c>
       <c r="L38" t="inlineStr"/>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>confirmado por una segunda fuente</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>Coinciden eth.blockscout.com y mainnet.gateway.tenderly.co.</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -43150,6 +43585,16 @@
           <t>blockscout:https://base.blockscout.com/api</t>
         </is>
       </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>una sola fuente</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>Una sola fuente: base.blockscout.com devolvió una lista incompleta.</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -43208,6 +43653,16 @@
         </is>
       </c>
       <c r="L40" t="inlineStr"/>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>confirmado por una segunda fuente</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>Coinciden polygon.blockscout.com y polygon.gateway.tenderly.co.</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -43262,6 +43717,16 @@
       </c>
       <c r="K41" t="inlineStr"/>
       <c r="L41" t="inlineStr"/>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>una sola fuente</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>Una sola fuente: no hay una segunda fuente gratuita para esta red.</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -43314,8 +43779,22 @@
           <t>bscscan list + RPC receipts</t>
         </is>
       </c>
-      <c r="K42" t="inlineStr"/>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>rpc:bsc-mainnet.nodereal.io/v1/***</t>
+        </is>
+      </c>
       <c r="L42" t="inlineStr"/>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>confirmado por una segunda fuente</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>Coinciden bscscan list + RPC receipts y bsc-mainnet.nodereal.io.</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -43374,6 +43853,16 @@
         </is>
       </c>
       <c r="L43" t="inlineStr"/>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>confirmado por una segunda fuente</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>Coinciden worldchain-mainnet.explorer.alchemy.com y worldchain-mainnet.gateway.tenderly.co.</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -43432,6 +43921,16 @@
         </is>
       </c>
       <c r="L44" t="inlineStr"/>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>confirmado por una segunda fuente</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>Coinciden celo.blockscout.com y celo.gateway.tenderly.co.</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -43481,11 +43980,25 @@
       </c>
       <c r="J45" t="inlineStr">
         <is>
+          <t>etherscan:https://api.etherscan.io/v2/api</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
           <t>rpc:hyperliquid-json-rpc.stakely.io,rpc.hypurrscan.io</t>
         </is>
       </c>
-      <c r="K45" t="inlineStr"/>
       <c r="L45" t="inlineStr"/>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>confirmado por una segunda fuente</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>Coinciden api.etherscan.io y hyperliquid-json-rpc.stakely.io,rpc.hypurrscan.io.</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -43540,6 +44053,16 @@
       </c>
       <c r="K46" t="inlineStr"/>
       <c r="L46" t="inlineStr"/>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>una sola fuente</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>Una sola fuente: no hay una segunda fuente gratuita para esta red.</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -43598,6 +44121,16 @@
         </is>
       </c>
       <c r="L47" t="inlineStr"/>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>confirmado por una segunda fuente</t>
+        </is>
+      </c>
+      <c r="N47" t="inlineStr">
+        <is>
+          <t>Coinciden eth.blockscout.com y mainnet.gateway.tenderly.co.</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -43656,6 +44189,16 @@
         </is>
       </c>
       <c r="L48" t="inlineStr"/>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>confirmado por una segunda fuente</t>
+        </is>
+      </c>
+      <c r="N48" t="inlineStr">
+        <is>
+          <t>Coinciden base.blockscout.com y mainnet.base.org.</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -43714,6 +44257,16 @@
         </is>
       </c>
       <c r="L49" t="inlineStr"/>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>confirmado por una segunda fuente</t>
+        </is>
+      </c>
+      <c r="N49" t="inlineStr">
+        <is>
+          <t>Coinciden polygon.blockscout.com y polygon.gateway.tenderly.co.</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -43768,6 +44321,16 @@
       </c>
       <c r="K50" t="inlineStr"/>
       <c r="L50" t="inlineStr"/>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>una sola fuente</t>
+        </is>
+      </c>
+      <c r="N50" t="inlineStr">
+        <is>
+          <t>Una sola fuente: no hay una segunda fuente gratuita para esta red.</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -43820,8 +44383,22 @@
           <t>bscscan list + RPC receipts</t>
         </is>
       </c>
-      <c r="K51" t="inlineStr"/>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>rpc:bsc-mainnet.nodereal.io/v1/***</t>
+        </is>
+      </c>
       <c r="L51" t="inlineStr"/>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>confirmado por una segunda fuente</t>
+        </is>
+      </c>
+      <c r="N51" t="inlineStr">
+        <is>
+          <t>Coinciden bscscan list + RPC receipts y bsc-mainnet.nodereal.io.</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -43880,6 +44457,16 @@
         </is>
       </c>
       <c r="L52" t="inlineStr"/>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>confirmado por una segunda fuente</t>
+        </is>
+      </c>
+      <c r="N52" t="inlineStr">
+        <is>
+          <t>Coinciden worldchain-mainnet.explorer.alchemy.com y worldchain-mainnet.gateway.tenderly.co.</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -43938,6 +44525,16 @@
         </is>
       </c>
       <c r="L53" t="inlineStr"/>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>confirmado por una segunda fuente</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr">
+        <is>
+          <t>Coinciden celo.blockscout.com y celo.gateway.tenderly.co.</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -43987,11 +44584,25 @@
       </c>
       <c r="J54" t="inlineStr">
         <is>
+          <t>etherscan:https://api.etherscan.io/v2/api</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
           <t>rpc:hyperliquid-json-rpc.stakely.io,rpc.hypurrscan.io</t>
         </is>
       </c>
-      <c r="K54" t="inlineStr"/>
       <c r="L54" t="inlineStr"/>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>confirmado por una segunda fuente</t>
+        </is>
+      </c>
+      <c r="N54" t="inlineStr">
+        <is>
+          <t>Coinciden api.etherscan.io y hyperliquid-json-rpc.stakely.io,rpc.hypurrscan.io.</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -44046,6 +44657,16 @@
       </c>
       <c r="K55" t="inlineStr"/>
       <c r="L55" t="inlineStr"/>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>una sola fuente</t>
+        </is>
+      </c>
+      <c r="N55" t="inlineStr">
+        <is>
+          <t>Una sola fuente: no hay una segunda fuente gratuita para esta red.</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">

--- a/data/closes/2026-09-30/paquete_cierre_2026-09-30.xlsx
+++ b/data/closes/2026-09-30/paquete_cierre_2026-09-30.xlsx
@@ -520,7 +520,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Corte: 30/09/2026 23:59:59 hora de Buenos Aires. Cierre anterior: 30/06/2026. Generado: 2026-10-03T18:09:23+00:00 (UTC).</t>
+          <t>Corte: 30/09/2026 23:59:59 hora de Buenos Aires. Cierre anterior: 30/06/2026. Generado: 2026-10-03T18:32:34+00:00 (UTC).</t>
         </is>
       </c>
     </row>
@@ -13483,7 +13483,7 @@
       </c>
       <c r="M171" s="6" t="inlineStr">
         <is>
-          <t>Salió por el puente el 29/07/2026 hacia Celo y no encontramos la emisión del otro lado (buscada hasta el bloque 79150197 de Celo).</t>
+          <t>Salió por el puente el 29/07/2026 hacia Celo y no encontramos la emisión del otro lado (buscada hasta el bloque 79151590 de Celo).</t>
         </is>
       </c>
     </row>
@@ -20954,7 +20954,7 @@
       </c>
       <c r="M303" s="6" t="inlineStr">
         <is>
-          <t>Salió por el puente el 02/09/2026 hacia Gnosis y no encontramos la emisión del otro lado (buscada hasta el bloque 48571094 de Gnosis).</t>
+          <t>Salió por el puente el 02/09/2026 hacia Gnosis y no encontramos la emisión del otro lado (buscada hasta el bloque 48571369 de Gnosis).</t>
         </is>
       </c>
     </row>
@@ -30365,7 +30365,7 @@
       </c>
       <c r="M465" s="6" t="inlineStr">
         <is>
-          <t>Salió por el puente el 14/09/2026 hacia Ethereum y no encontramos la emisión del otro lado (buscada hasta el bloque 26113511 de Ethereum).</t>
+          <t>Salió por el puente el 14/09/2026 hacia Ethereum y no encontramos la emisión del otro lado (buscada hasta el bloque 26113625 de Ethereum).</t>
         </is>
       </c>
     </row>
@@ -44687,7 +44687,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C15"/>
+  <dimension ref="A1:C16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="70" customWidth="1" min="1" max="1"/>
@@ -44834,7 +44834,7 @@
     <row r="9">
       <c r="A9" s="7" t="inlineStr">
         <is>
-          <t>Una quema es rescate primario si quien quema sus propios tokens tiene permiso de emisión (MINTER_ROLE) en el LimitedMinter de esa red, leído en el bloque de la quema.</t>
+          <t>Una emisión también es primaria si la transacción va directo al contrato del token y quien la envía tiene permiso de emisión (MINTER_ROLE) en el token, leído en el bloque de la emisión. Si pasa por una billetera u otro contrato, no se puede probar quién emitió y queda para el agente de excepciones.</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -44844,14 +44844,14 @@
       </c>
       <c r="C9" s="7" t="inlineStr">
         <is>
-          <t>Lectura onchain de hasRole(MINTER_ROLE, cuenta) en el LimitedMinter verificado.</t>
+          <t>Lectura onchain de hasRole(MINTER_ROLE, cuenta) en el contrato del token (LatamStable).</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="7" t="inlineStr">
         <is>
-          <t>Lo que no encaja en ninguna de estas reglas queda sin clasificar. No se adivina.</t>
+          <t>Una quema es rescate primario si quien quema sus propios tokens tiene permiso de emisión (MINTER_ROLE) en el LimitedMinter de esa red, leído en el bloque de la quema.</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -44861,31 +44861,31 @@
       </c>
       <c r="C10" s="7" t="inlineStr">
         <is>
-          <t>Regla del motor.</t>
+          <t>Lectura onchain de hasRole(MINTER_ROLE, cuenta) en el LimitedMinter verificado.</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="7" t="inlineStr">
         <is>
-          <t>La cantidad en circulación es la suma de totalSupply() en las redes revisadas, sin excluir billeteras.</t>
+          <t>Lo que no encaja en ninguna de estas reglas queda sin clasificar. No se adivina.</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>inferida</t>
+          <t>documentada</t>
         </is>
       </c>
       <c r="C11" s="7" t="inlineStr">
         <is>
-          <t>Reproduce las 9 cifras certificadas publicadas (data/golden/verification.json).</t>
+          <t>Regla del motor.</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="7" t="inlineStr">
         <is>
-          <t>La comparación con las cifras certificadas se hace en tokens enteros.</t>
+          <t>La cantidad en circulación es la suma de totalSupply() en las redes revisadas, sin excluir billeteras.</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -44895,14 +44895,14 @@
       </c>
       <c r="C12" s="7" t="inlineStr">
         <is>
-          <t>Regla única para las 9 certificaciones. Decisión de Máximo Sckell.</t>
+          <t>Reproduce las 9 cifras certificadas publicadas (data/golden/verification.json).</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="7" t="inlineStr">
         <is>
-          <t>El corte es a las 23:59:59 hora de Buenos Aires del último día del trimestre.</t>
+          <t>La comparación con las cifras certificadas se hace en tokens enteros.</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -44912,39 +44912,56 @@
       </c>
       <c r="C13" s="7" t="inlineStr">
         <is>
-          <t>En los cortes certificados, 23:59:59 de Buenos Aires y de UTC dan el mismo resultado.</t>
+          <t>Regla única para las 9 certificaciones. Decisión de Máximo Sckell.</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="7" t="inlineStr">
         <is>
-          <t>Las redes revisadas son una lista escrita de redes EVM candidatas, cruzada con CoinGecko y con las redes que nombran los certificados.</t>
+          <t>El corte es a las 23:59:59 hora de Buenos Aires del último día del trimestre.</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>documentada</t>
+          <t>inferida</t>
         </is>
       </c>
       <c r="C14" s="7" t="inlineStr">
         <is>
-          <t>config/chains.yaml, data/discovery.json y data/sources/coingecko_platforms.json.</t>
+          <t>En los cortes certificados, 23:59:59 de Buenos Aires y de UTC dan el mismo resultado.</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="7" t="inlineStr">
         <is>
+          <t>Las redes revisadas son una lista escrita de redes EVM candidatas, cruzada con CoinGecko y con las redes que nombran los certificados.</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>documentada</t>
+        </is>
+      </c>
+      <c r="C15" s="7" t="inlineStr">
+        <is>
+          <t>config/chains.yaml, data/discovery.json y data/sources/coingecko_platforms.json.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="7" t="inlineStr">
+        <is>
           <t>wUYU no se incluye: existe en las mismas redes, pero lo creó una fábrica pública y no hay evidencia de que sea de Ripio.</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
+      <c r="B16" t="inlineStr">
         <is>
           <t>hipótesis</t>
         </is>
       </c>
-      <c r="C15" s="7" t="inlineStr">
+      <c r="C16" s="7" t="inlineStr">
         <is>
           <t>data/discovery.json</t>
         </is>
